--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -1354,7 +1354,7 @@
     <t>0.9872,0.0068,0.0021,0.0004</t>
   </si>
   <si>
-    <t>0.5397,0.3327,0.0759,0.0016</t>
+    <t>0.5397,0.3326,0.0759,0.0016</t>
   </si>
   <si>
     <t>0.9849,0.0025,0.0045,0.0004</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="528">
   <si>
     <t>Filename</t>
   </si>
@@ -820,22 +820,31 @@
     <t>0,1,0,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,1,0</t>
   </si>
   <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9568,0.0045,0.0112,0.0019</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9568,0.0046,0.0113,0.0019</t>
   </si>
   <si>
     <t>0.0061,0.0032,0.0001,0.9982</t>
   </si>
   <si>
-    <t>0.9017,0.0023,0.0004,0.0384</t>
-  </si>
-  <si>
-    <t>0.2552,0.0008,0.0013,0.7543</t>
+    <t>0.9012,0.0023,0.0004,0.0387</t>
+  </si>
+  <si>
+    <t>0.2539,0.0008,0.0013,0.7561</t>
   </si>
   <si>
     <t>0.9894,0.0030,0.0019,0.0008</t>
@@ -850,7 +859,7 @@
     <t>0.9916,0.0017,0.0016,0.0004</t>
   </si>
   <si>
-    <t>0.9716,0.0330,0.0012,0.0005</t>
+    <t>0.9715,0.0331,0.0012,0.0005</t>
   </si>
   <si>
     <t>0.9875,0.0072,0.0015,0.0012</t>
@@ -862,19 +871,19 @@
     <t>0.9906,0.0022,0.0019,0.0006</t>
   </si>
   <si>
-    <t>0.8055,0.0077,0.1666,0.0020</t>
+    <t>0.8053,0.0078,0.1668,0.0020</t>
   </si>
   <si>
     <t>0.0139,0.0672,0.9521,0.0029</t>
   </si>
   <si>
-    <t>0.1492,0.0013,0.9019,0.0004</t>
-  </si>
-  <si>
-    <t>0.0587,0.0071,0.9456,0.0019</t>
-  </si>
-  <si>
-    <t>0.4642,0.0017,0.6005,0.0005</t>
+    <t>0.1489,0.0013,0.9021,0.0004</t>
+  </si>
+  <si>
+    <t>0.0587,0.0071,0.9457,0.0019</t>
+  </si>
+  <si>
+    <t>0.4635,0.0017,0.6012,0.0005</t>
   </si>
   <si>
     <t>0.0011,0.9987,0.0116,0.0003</t>
@@ -883,37 +892,37 @@
     <t>0.0018,0.9967,0.0047,0.0020</t>
   </si>
   <si>
-    <t>0.2175,0.9104,0.0031,0.0000</t>
+    <t>0.2173,0.9105,0.0031,0.0000</t>
   </si>
   <si>
     <t>0.0029,0.9941,0.0111,0.0046</t>
   </si>
   <si>
-    <t>0.0014,0.9990,0.0486,0.0000</t>
-  </si>
-  <si>
-    <t>0.5888,0.0006,0.5072,0.0007</t>
-  </si>
-  <si>
-    <t>0.0846,0.0109,0.9183,0.0068</t>
+    <t>0.0014,0.9990,0.0485,0.0000</t>
+  </si>
+  <si>
+    <t>0.5886,0.0006,0.5074,0.0007</t>
+  </si>
+  <si>
+    <t>0.0844,0.0109,0.9184,0.0068</t>
   </si>
   <si>
     <t>0.0263,0.0002,0.9874,0.0001</t>
   </si>
   <si>
-    <t>0.0161,0.0042,0.9839,0.0009</t>
+    <t>0.0160,0.0042,0.9839,0.0009</t>
   </si>
   <si>
     <t>0.0222,0.0014,0.9842,0.0008</t>
   </si>
   <si>
-    <t>0.0898,0.0008,0.9450,0.0005</t>
+    <t>0.0896,0.0008,0.9451,0.0005</t>
   </si>
   <si>
     <t>0.0130,0.0007,0.9902,0.0006</t>
   </si>
   <si>
-    <t>0.5889,0.4602,0.0458,0.0017</t>
+    <t>0.5886,0.4610,0.0456,0.0017</t>
   </si>
   <si>
     <t>0.9431,0.0538,0.0067,0.0016</t>
@@ -922,34 +931,34 @@
     <t>0.0020,0.0002,0.9980,0.0003</t>
   </si>
   <si>
-    <t>0.0107,0.3923,0.8636,0.0016</t>
-  </si>
-  <si>
-    <t>0.9285,0.0019,0.0486,0.0009</t>
-  </si>
-  <si>
-    <t>0.8334,0.0079,0.1264,0.0021</t>
-  </si>
-  <si>
-    <t>0.2744,0.8523,0.0181,0.0010</t>
-  </si>
-  <si>
-    <t>0.0121,0.9653,0.4633,0.0041</t>
-  </si>
-  <si>
-    <t>0.0006,0.9096,0.9547,0.0002</t>
+    <t>0.0107,0.3919,0.8636,0.0016</t>
+  </si>
+  <si>
+    <t>0.9283,0.0019,0.0487,0.0009</t>
+  </si>
+  <si>
+    <t>0.8332,0.0079,0.1266,0.0021</t>
+  </si>
+  <si>
+    <t>0.2741,0.8524,0.0180,0.0010</t>
+  </si>
+  <si>
+    <t>0.0121,0.9653,0.4636,0.0041</t>
+  </si>
+  <si>
+    <t>0.0006,0.9095,0.9547,0.0002</t>
   </si>
   <si>
     <t>0.0010,0.0052,0.9962,0.0039</t>
   </si>
   <si>
-    <t>0.0312,0.0303,0.9444,0.0124</t>
-  </si>
-  <si>
-    <t>0.0797,0.0007,0.8695,0.0485</t>
-  </si>
-  <si>
-    <t>0.0010,0.9336,0.8434,0.0008</t>
+    <t>0.0312,0.0302,0.9445,0.0124</t>
+  </si>
+  <si>
+    <t>0.0796,0.0007,0.8696,0.0486</t>
+  </si>
+  <si>
+    <t>0.0010,0.9335,0.8435,0.0008</t>
   </si>
   <si>
     <t>0.0005,0.9953,0.0100,0.0012</t>
@@ -958,7 +967,7 @@
     <t>0.0057,0.0171,0.9876,0.0019</t>
   </si>
   <si>
-    <t>0.0007,0.5951,0.0016,0.9768</t>
+    <t>0.0007,0.5959,0.0016,0.9768</t>
   </si>
   <si>
     <t>0.0001,0.9997,0.0003,0.0001</t>
@@ -973,16 +982,16 @@
     <t>0.0014,0.0268,0.9913,0.0023</t>
   </si>
   <si>
-    <t>0.0009,0.1444,0.9900,0.0017</t>
+    <t>0.0009,0.1443,0.9900,0.0017</t>
   </si>
   <si>
     <t>0.0125,0.0029,0.9852,0.0014</t>
   </si>
   <si>
-    <t>0.0428,0.0001,0.9837,0.0000</t>
-  </si>
-  <si>
-    <t>0.0210,0.0023,0.9826,0.0006</t>
+    <t>0.0427,0.0001,0.9838,0.0000</t>
+  </si>
+  <si>
+    <t>0.0209,0.0023,0.9826,0.0006</t>
   </si>
   <si>
     <t>0.0267,0.0142,0.9608,0.0035</t>
@@ -997,7 +1006,7 @@
     <t>0.9708,0.0152,0.0056,0.0024</t>
   </si>
   <si>
-    <t>0.2506,0.0008,0.7782,0.0010</t>
+    <t>0.2503,0.0008,0.7784,0.0010</t>
   </si>
   <si>
     <t>0.9775,0.0011,0.0120,0.0006</t>
@@ -1015,7 +1024,7 @@
     <t>0.0014,0.0188,0.9972,0.0002</t>
   </si>
   <si>
-    <t>0.0042,0.0502,0.9881,0.0024</t>
+    <t>0.0042,0.0501,0.9881,0.0024</t>
   </si>
   <si>
     <t>0.0003,0.9730,0.9584,0.0003</t>
@@ -1024,16 +1033,16 @@
     <t>0.0001,0.0004,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0073,0.9951,0.0042,0.0001</t>
+    <t>0.0073,0.9952,0.0042,0.0001</t>
   </si>
   <si>
     <t>0.0004,0.9991,0.0059,0.0001</t>
   </si>
   <si>
-    <t>0.9623,0.0020,0.0250,0.0003</t>
-  </si>
-  <si>
-    <t>0.1705,0.2341,0.5751,0.0044</t>
+    <t>0.9623,0.0020,0.0251,0.0003</t>
+  </si>
+  <si>
+    <t>0.1706,0.2341,0.5749,0.0044</t>
   </si>
   <si>
     <t>0.0078,0.0075,0.9877,0.0015</t>
@@ -1045,7 +1054,7 @@
     <t>0.0003,0.9545,0.9713,0.0001</t>
   </si>
   <si>
-    <t>0.0001,0.9986,0.4494,0.0000</t>
+    <t>0.0001,0.9986,0.4493,0.0000</t>
   </si>
   <si>
     <t>0.0004,0.9678,0.9509,0.0004</t>
@@ -1069,49 +1078,49 @@
     <t>0.0003,0.0011,0.0009,0.9999</t>
   </si>
   <si>
-    <t>0.0004,0.9966,0.5866,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9214,0.9728,0.0003</t>
+    <t>0.0004,0.9966,0.5863,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9211,0.9729,0.0003</t>
   </si>
   <si>
     <t>0.0005,0.9714,0.8000,0.0006</t>
   </si>
   <si>
-    <t>0.0002,0.9017,0.9879,0.0002</t>
+    <t>0.0002,0.9016,0.9879,0.0002</t>
   </si>
   <si>
     <t>0.0000,0.9936,0.9723,0.0000</t>
   </si>
   <si>
-    <t>0.0007,0.9892,0.5095,0.0003</t>
+    <t>0.0007,0.9892,0.5094,0.0003</t>
   </si>
   <si>
     <t>0.9903,0.0074,0.0008,0.0005</t>
   </si>
   <si>
-    <t>0.9586,0.0237,0.0075,0.0018</t>
-  </si>
-  <si>
-    <t>0.9595,0.0492,0.0018,0.0006</t>
+    <t>0.9586,0.0238,0.0075,0.0018</t>
+  </si>
+  <si>
+    <t>0.9595,0.0493,0.0018,0.0006</t>
   </si>
   <si>
     <t>0.9914,0.0051,0.0012,0.0005</t>
   </si>
   <si>
-    <t>0.9861,0.0086,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.9875,0.0068,0.0019,0.0024</t>
-  </si>
-  <si>
-    <t>0.9525,0.0053,0.0229,0.0022</t>
-  </si>
-  <si>
-    <t>0.9687,0.0026,0.0061,0.0006</t>
-  </si>
-  <si>
-    <t>0.9912,0.0022,0.0016,0.0009</t>
+    <t>0.9861,0.0087,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.9875,0.0069,0.0019,0.0024</t>
+  </si>
+  <si>
+    <t>0.9524,0.0053,0.0229,0.0022</t>
+  </si>
+  <si>
+    <t>0.9687,0.0025,0.0061,0.0006</t>
+  </si>
+  <si>
+    <t>0.9911,0.0022,0.0016,0.0009</t>
   </si>
   <si>
     <t>0.9879,0.0110,0.0015,0.0010</t>
@@ -1126,10 +1135,10 @@
     <t>0.9746,0.0114,0.0042,0.0042</t>
   </si>
   <si>
-    <t>0.9942,0.0028,0.0008,0.0011</t>
-  </si>
-  <si>
-    <t>0.9925,0.0036,0.0009,0.0009</t>
+    <t>0.9941,0.0028,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.9925,0.0037,0.0009,0.0009</t>
   </si>
   <si>
     <t>0.9905,0.0024,0.0018,0.0008</t>
@@ -1141,7 +1150,7 @@
     <t>0.0535,0.0038,0.9561,0.0019</t>
   </si>
   <si>
-    <t>0.9675,0.0002,0.0434,0.0000</t>
+    <t>0.9674,0.0002,0.0435,0.0000</t>
   </si>
   <si>
     <t>0.0589,0.0016,0.9600,0.0007</t>
@@ -1153,34 +1162,34 @@
     <t>0.0003,0.9998,0.0014,0.0000</t>
   </si>
   <si>
-    <t>0.6067,0.5297,0.0021,0.0004</t>
-  </si>
-  <si>
-    <t>0.1997,0.8776,0.0134,0.0017</t>
-  </si>
-  <si>
-    <t>0.0004,0.9995,0.0012,0.0001</t>
+    <t>0.6060,0.5305,0.0021,0.0004</t>
+  </si>
+  <si>
+    <t>0.1993,0.8779,0.0134,0.0017</t>
+  </si>
+  <si>
+    <t>0.0004,0.9995,0.0011,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0005,0.0000</t>
   </si>
   <si>
-    <t>0.9024,0.1638,0.0080,0.0006</t>
-  </si>
-  <si>
-    <t>0.1709,0.0210,0.8172,0.0073</t>
-  </si>
-  <si>
-    <t>0.0730,0.0094,0.9225,0.0076</t>
-  </si>
-  <si>
-    <t>0.4507,0.0083,0.5596,0.0018</t>
-  </si>
-  <si>
-    <t>0.1856,0.0127,0.8335,0.0084</t>
-  </si>
-  <si>
-    <t>0.0010,0.6844,0.8988,0.0509</t>
+    <t>0.9022,0.1641,0.0080,0.0006</t>
+  </si>
+  <si>
+    <t>0.1708,0.0211,0.8173,0.0073</t>
+  </si>
+  <si>
+    <t>0.0729,0.0094,0.9227,0.0075</t>
+  </si>
+  <si>
+    <t>0.4504,0.0083,0.5600,0.0018</t>
+  </si>
+  <si>
+    <t>0.1852,0.0127,0.8339,0.0084</t>
+  </si>
+  <si>
+    <t>0.0010,0.6843,0.8989,0.0509</t>
   </si>
   <si>
     <t>0.0001,0.9998,0.0029,0.0000</t>
@@ -1195,19 +1204,19 @@
     <t>0.0001,0.9983,0.0208,0.0006</t>
   </si>
   <si>
-    <t>0.0020,0.9966,0.2418,0.0003</t>
-  </si>
-  <si>
-    <t>0.2605,0.7397,0.1092,0.0044</t>
-  </si>
-  <si>
-    <t>0.0324,0.9587,0.0525,0.0118</t>
+    <t>0.0020,0.9966,0.2414,0.0003</t>
+  </si>
+  <si>
+    <t>0.2601,0.7401,0.1093,0.0044</t>
+  </si>
+  <si>
+    <t>0.0323,0.9588,0.0525,0.0118</t>
   </si>
   <si>
     <t>0.9945,0.0005,0.0012,0.0004</t>
   </si>
   <si>
-    <t>0.9844,0.0100,0.0008,0.0011</t>
+    <t>0.9844,0.0101,0.0008,0.0011</t>
   </si>
   <si>
     <t>0.9844,0.0053,0.0024,0.0029</t>
@@ -1219,37 +1228,37 @@
     <t>0.9928,0.0035,0.0011,0.0014</t>
   </si>
   <si>
-    <t>0.9617,0.0010,0.0104,0.0036</t>
+    <t>0.9616,0.0010,0.0104,0.0036</t>
   </si>
   <si>
     <t>0.9888,0.0018,0.0026,0.0016</t>
   </si>
   <si>
-    <t>0.9913,0.0009,0.0024,0.0007</t>
+    <t>0.9912,0.0009,0.0024,0.0007</t>
   </si>
   <si>
     <t>0.0006,0.9609,0.9267,0.0003</t>
   </si>
   <si>
-    <t>0.0002,0.6981,0.9935,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0368,0.9978,0.0006</t>
+    <t>0.0003,0.6976,0.9935,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0366,0.9978,0.0006</t>
   </si>
   <si>
     <t>0.0090,0.0140,0.9887,0.0007</t>
   </si>
   <si>
-    <t>0.9594,0.0016,0.0295,0.0003</t>
-  </si>
-  <si>
-    <t>0.3402,0.3581,0.1665,0.0097</t>
-  </si>
-  <si>
-    <t>0.1568,0.0008,0.8917,0.0017</t>
-  </si>
-  <si>
-    <t>0.6630,0.0090,0.3159,0.0035</t>
+    <t>0.9593,0.0016,0.0295,0.0003</t>
+  </si>
+  <si>
+    <t>0.3396,0.3588,0.1665,0.0097</t>
+  </si>
+  <si>
+    <t>0.1569,0.0008,0.8917,0.0017</t>
+  </si>
+  <si>
+    <t>0.6624,0.0090,0.3166,0.0035</t>
   </si>
   <si>
     <t>0.0040,0.0001,0.0006,0.9994</t>
@@ -1267,22 +1276,22 @@
     <t>0.0003,0.9887,0.8986,0.0001</t>
   </si>
   <si>
-    <t>0.9755,0.0011,0.0114,0.0010</t>
-  </si>
-  <si>
-    <t>0.0183,0.9760,0.0169,0.0076</t>
-  </si>
-  <si>
-    <t>0.9873,0.0007,0.0050,0.0005</t>
+    <t>0.9756,0.0011,0.0114,0.0010</t>
+  </si>
+  <si>
+    <t>0.0183,0.9761,0.0169,0.0076</t>
+  </si>
+  <si>
+    <t>0.9873,0.0008,0.0050,0.0005</t>
   </si>
   <si>
     <t>0.0162,0.9853,0.0102,0.0017</t>
   </si>
   <si>
-    <t>0.9890,0.0020,0.0014,0.0012</t>
-  </si>
-  <si>
-    <t>0.1099,0.0000,0.9570,0.0000</t>
+    <t>0.9890,0.0020,0.0014,0.0013</t>
+  </si>
+  <si>
+    <t>0.1102,0.0000,0.9569,0.0000</t>
   </si>
   <si>
     <t>0.0775,0.0001,0.9556,0.0000</t>
@@ -1291,28 +1300,28 @@
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.8601,0.0005,0.0898,0.0062</t>
-  </si>
-  <si>
-    <t>0.9491,0.0072,0.0138,0.0041</t>
-  </si>
-  <si>
-    <t>0.5816,0.2647,0.0636,0.0019</t>
+    <t>0.8599,0.0005,0.0899,0.0062</t>
+  </si>
+  <si>
+    <t>0.9490,0.0072,0.0138,0.0041</t>
+  </si>
+  <si>
+    <t>0.5814,0.2651,0.0635,0.0019</t>
   </si>
   <si>
     <t>0.9869,0.0014,0.0049,0.0003</t>
   </si>
   <si>
-    <t>0.9246,0.0469,0.0144,0.0042</t>
-  </si>
-  <si>
-    <t>0.1053,0.8785,0.0638,0.0126</t>
+    <t>0.9245,0.0470,0.0144,0.0042</t>
+  </si>
+  <si>
+    <t>0.1052,0.8787,0.0637,0.0126</t>
   </si>
   <si>
     <t>0.9176,0.0124,0.0502,0.0009</t>
   </si>
   <si>
-    <t>0.7609,0.0451,0.1470,0.0032</t>
+    <t>0.7605,0.0451,0.1473,0.0032</t>
   </si>
   <si>
     <t>0.9927,0.0022,0.0013,0.0003</t>
@@ -1330,7 +1339,7 @@
     <t>0.9905,0.0030,0.0017,0.0003</t>
   </si>
   <si>
-    <t>0.9920,0.0030,0.0013,0.0004</t>
+    <t>0.9920,0.0030,0.0014,0.0004</t>
   </si>
   <si>
     <t>0.9860,0.0042,0.0027,0.0008</t>
@@ -1339,46 +1348,46 @@
     <t>0.9899,0.0010,0.0028,0.0006</t>
   </si>
   <si>
-    <t>0.6434,0.4363,0.0135,0.0027</t>
-  </si>
-  <si>
-    <t>0.4752,0.6382,0.0132,0.0028</t>
-  </si>
-  <si>
-    <t>0.7600,0.2697,0.0071,0.0022</t>
-  </si>
-  <si>
-    <t>0.6859,0.0412,0.2034,0.0014</t>
+    <t>0.6431,0.4368,0.0135,0.0027</t>
+  </si>
+  <si>
+    <t>0.4746,0.6388,0.0133,0.0028</t>
+  </si>
+  <si>
+    <t>0.7592,0.2707,0.0072,0.0022</t>
+  </si>
+  <si>
+    <t>0.6854,0.0412,0.2039,0.0014</t>
   </si>
   <si>
     <t>0.9872,0.0068,0.0021,0.0004</t>
   </si>
   <si>
-    <t>0.5397,0.3326,0.0759,0.0016</t>
+    <t>0.5395,0.3330,0.0759,0.0016</t>
   </si>
   <si>
     <t>0.9849,0.0025,0.0045,0.0004</t>
   </si>
   <si>
-    <t>0.9640,0.0262,0.0077,0.0016</t>
+    <t>0.9639,0.0262,0.0077,0.0016</t>
   </si>
   <si>
     <t>0.0062,0.0036,0.9926,0.0003</t>
   </si>
   <si>
-    <t>0.8014,0.0792,0.0755,0.0019</t>
+    <t>0.8008,0.0794,0.0757,0.0019</t>
   </si>
   <si>
     <t>0.0006,0.0006,0.9993,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.4710,0.9818,0.0021</t>
+    <t>0.0002,0.4701,0.9818,0.0021</t>
   </si>
   <si>
     <t>0.0133,0.0025,0.9860,0.0017</t>
   </si>
   <si>
-    <t>0.0016,0.7725,0.8795,0.0006</t>
+    <t>0.0016,0.7722,0.8796,0.0006</t>
   </si>
   <si>
     <t>0.0016,0.0022,0.9977,0.0001</t>
@@ -1390,13 +1399,13 @@
     <t>0.0107,0.0009,0.9920,0.0003</t>
   </si>
   <si>
-    <t>0.0791,0.0066,0.9332,0.0025</t>
-  </si>
-  <si>
-    <t>0.1409,0.0020,0.8998,0.0009</t>
-  </si>
-  <si>
-    <t>0.4364,0.0968,0.3828,0.0120</t>
+    <t>0.0790,0.0065,0.9334,0.0025</t>
+  </si>
+  <si>
+    <t>0.1406,0.0020,0.9000,0.0009</t>
+  </si>
+  <si>
+    <t>0.4359,0.0971,0.3828,0.0120</t>
   </si>
   <si>
     <t>0.0226,0.0163,0.9636,0.0034</t>
@@ -1405,64 +1414,64 @@
     <t>0.0094,0.0268,0.9779,0.0006</t>
   </si>
   <si>
-    <t>0.0808,0.0070,0.9212,0.0042</t>
-  </si>
-  <si>
-    <t>0.1205,0.0042,0.9041,0.0023</t>
-  </si>
-  <si>
-    <t>0.3694,0.0282,0.6111,0.0050</t>
-  </si>
-  <si>
-    <t>0.4544,0.7293,0.0029,0.0001</t>
+    <t>0.0807,0.0070,0.9213,0.0042</t>
+  </si>
+  <si>
+    <t>0.1201,0.0042,0.9044,0.0023</t>
+  </si>
+  <si>
+    <t>0.3689,0.0282,0.6118,0.0050</t>
+  </si>
+  <si>
+    <t>0.4541,0.7296,0.0029,0.0001</t>
   </si>
   <si>
     <t>0.0053,0.9959,0.0050,0.0004</t>
   </si>
   <si>
-    <t>0.0982,0.9355,0.0157,0.0017</t>
-  </si>
-  <si>
-    <t>0.9386,0.0406,0.0078,0.0008</t>
-  </si>
-  <si>
-    <t>0.4144,0.6837,0.0078,0.0011</t>
-  </si>
-  <si>
-    <t>0.1481,0.8708,0.0181,0.0016</t>
-  </si>
-  <si>
-    <t>0.9442,0.0162,0.0164,0.0012</t>
-  </si>
-  <si>
-    <t>0.3479,0.0514,0.5826,0.0326</t>
-  </si>
-  <si>
-    <t>0.1394,0.0046,0.8695,0.0090</t>
-  </si>
-  <si>
-    <t>0.2962,0.0082,0.6935,0.0041</t>
+    <t>0.0980,0.9357,0.0157,0.0017</t>
+  </si>
+  <si>
+    <t>0.9385,0.0407,0.0078,0.0008</t>
+  </si>
+  <si>
+    <t>0.4137,0.6844,0.0078,0.0011</t>
+  </si>
+  <si>
+    <t>0.1478,0.8711,0.0181,0.0016</t>
+  </si>
+  <si>
+    <t>0.9442,0.0163,0.0164,0.0012</t>
+  </si>
+  <si>
+    <t>0.3473,0.0515,0.5832,0.0326</t>
+  </si>
+  <si>
+    <t>0.1392,0.0046,0.8697,0.0090</t>
+  </si>
+  <si>
+    <t>0.2965,0.0083,0.6930,0.0041</t>
   </si>
   <si>
     <t>0.0109,0.0012,0.9900,0.0008</t>
   </si>
   <si>
-    <t>0.0845,0.0062,0.9224,0.0022</t>
-  </si>
-  <si>
-    <t>0.0492,0.0243,0.9160,0.0021</t>
-  </si>
-  <si>
-    <t>0.0055,0.0123,0.9915,0.0014</t>
+    <t>0.0846,0.0062,0.9224,0.0022</t>
+  </si>
+  <si>
+    <t>0.0491,0.0243,0.9160,0.0021</t>
+  </si>
+  <si>
+    <t>0.0055,0.0122,0.9915,0.0014</t>
   </si>
   <si>
     <t>0.0115,0.0019,0.9915,0.0002</t>
   </si>
   <si>
-    <t>0.9870,0.0015,0.0037,0.0009</t>
-  </si>
-  <si>
-    <t>0.9690,0.0174,0.0060,0.0030</t>
+    <t>0.9869,0.0015,0.0037,0.0009</t>
+  </si>
+  <si>
+    <t>0.9690,0.0175,0.0060,0.0030</t>
   </si>
   <si>
     <t>0.9465,0.0263,0.0119,0.0050</t>
@@ -1471,13 +1480,13 @@
     <t>0.9769,0.0202,0.0026,0.0019</t>
   </si>
   <si>
-    <t>0.9650,0.0199,0.0058,0.0033</t>
-  </si>
-  <si>
-    <t>0.9690,0.0191,0.0043,0.0025</t>
-  </si>
-  <si>
-    <t>0.9770,0.0094,0.0040,0.0021</t>
+    <t>0.9649,0.0199,0.0058,0.0033</t>
+  </si>
+  <si>
+    <t>0.9690,0.0192,0.0042,0.0025</t>
+  </si>
+  <si>
+    <t>0.9770,0.0095,0.0040,0.0021</t>
   </si>
   <si>
     <t>0.9837,0.0017,0.0053,0.0008</t>
@@ -1486,10 +1495,10 @@
     <t>0.0112,0.0009,0.9914,0.0004</t>
   </si>
   <si>
-    <t>0.0542,0.0478,0.9140,0.0019</t>
-  </si>
-  <si>
-    <t>0.2508,0.0192,0.7428,0.0147</t>
+    <t>0.0542,0.0479,0.9140,0.0019</t>
+  </si>
+  <si>
+    <t>0.2506,0.0192,0.7430,0.0147</t>
   </si>
   <si>
     <t>0.0009,0.0006,0.9991,0.0000</t>
@@ -1498,13 +1507,13 @@
     <t>0.0003,0.0071,0.9987,0.0005</t>
   </si>
   <si>
-    <t>0.0072,0.1654,0.9581,0.0010</t>
+    <t>0.0072,0.1653,0.9581,0.0010</t>
   </si>
   <si>
     <t>0.0001,0.0002,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0284,0.0112,0.9677,0.0012</t>
+    <t>0.0283,0.0112,0.9677,0.0012</t>
   </si>
   <si>
     <t>0.0000,0.0002,1.0000,0.0000</t>
@@ -1513,13 +1522,13 @@
     <t>0.0042,0.0202,0.9903,0.0014</t>
   </si>
   <si>
-    <t>0.0325,0.0364,0.9387,0.0053</t>
-  </si>
-  <si>
-    <t>0.6964,0.0042,0.3097,0.0036</t>
-  </si>
-  <si>
-    <t>0.7775,0.0012,0.2091,0.0025</t>
+    <t>0.0324,0.0364,0.9387,0.0053</t>
+  </si>
+  <si>
+    <t>0.6960,0.0042,0.3102,0.0036</t>
+  </si>
+  <si>
+    <t>0.7769,0.0012,0.2099,0.0025</t>
   </si>
   <si>
     <t>0.9486,0.0076,0.0237,0.0004</t>
@@ -1528,67 +1537,67 @@
     <t>0.9869,0.0079,0.0012,0.0006</t>
   </si>
   <si>
-    <t>0.9708,0.0332,0.0020,0.0008</t>
-  </si>
-  <si>
-    <t>0.9800,0.0106,0.0031,0.0014</t>
-  </si>
-  <si>
-    <t>0.9081,0.0667,0.0126,0.0017</t>
+    <t>0.9707,0.0333,0.0020,0.0008</t>
+  </si>
+  <si>
+    <t>0.9799,0.0106,0.0031,0.0014</t>
+  </si>
+  <si>
+    <t>0.9080,0.0668,0.0126,0.0017</t>
   </si>
   <si>
     <t>0.9871,0.0026,0.0027,0.0007</t>
   </si>
   <si>
-    <t>0.9574,0.0395,0.0031,0.0012</t>
+    <t>0.9573,0.0396,0.0031,0.0012</t>
   </si>
   <si>
     <t>0.9835,0.0089,0.0031,0.0011</t>
   </si>
   <si>
-    <t>0.9690,0.0096,0.0069,0.0025</t>
-  </si>
-  <si>
-    <t>0.0070,0.1012,0.9537,0.0016</t>
-  </si>
-  <si>
-    <t>0.0016,0.0181,0.9967,0.0003</t>
+    <t>0.9690,0.0097,0.0069,0.0025</t>
+  </si>
+  <si>
+    <t>0.0070,0.1011,0.9537,0.0016</t>
+  </si>
+  <si>
+    <t>0.0016,0.0181,0.9967,0.0002</t>
   </si>
   <si>
     <t>0.0033,0.0066,0.9950,0.0002</t>
   </si>
   <si>
-    <t>0.0177,0.0875,0.9298,0.0013</t>
-  </si>
-  <si>
-    <t>0.0149,0.0010,0.9904,0.0003</t>
-  </si>
-  <si>
-    <t>0.6260,0.0157,0.0981,0.0519</t>
-  </si>
-  <si>
-    <t>0.1170,0.0061,0.9040,0.0063</t>
-  </si>
-  <si>
-    <t>0.0010,0.0016,0.9971,0.0021</t>
-  </si>
-  <si>
-    <t>0.9370,0.0004,0.0008,0.0317</t>
+    <t>0.0177,0.0874,0.9298,0.0013</t>
+  </si>
+  <si>
+    <t>0.0148,0.0010,0.9904,0.0003</t>
+  </si>
+  <si>
+    <t>0.6258,0.0158,0.0980,0.0520</t>
+  </si>
+  <si>
+    <t>0.1167,0.0061,0.9042,0.0063</t>
+  </si>
+  <si>
+    <t>0.0010,0.0016,0.9971,0.0020</t>
+  </si>
+  <si>
+    <t>0.9368,0.0004,0.0008,0.0319</t>
   </si>
   <si>
     <t>0.0004,0.0045,0.0003,0.9998</t>
   </si>
   <si>
-    <t>0.0386,0.0004,0.0007,0.9917</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.0295,0.9998</t>
+    <t>0.0384,0.0004,0.0007,0.9917</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.0294,0.9998</t>
   </si>
   <si>
     <t>0.0001,0.0006,0.0011,0.9999</t>
   </si>
   <si>
-    <t>0.5785,0.0105,0.0139,0.3057</t>
+    <t>0.5776,0.0105,0.0139,0.3065</t>
   </si>
 </sst>
 </file>
@@ -1974,7 +1983,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1988,7 +1997,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2002,7 +2011,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2016,7 +2025,7 @@
         <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2030,7 +2039,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2044,7 +2053,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2058,7 +2067,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2072,7 +2081,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2086,7 +2095,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2100,7 +2109,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2114,7 +2123,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2128,7 +2137,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2142,7 +2151,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2156,7 +2165,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2170,7 +2179,7 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2184,7 +2193,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2198,7 +2207,7 @@
         <v>266</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2212,7 +2221,7 @@
         <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2226,7 +2235,7 @@
         <v>267</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2240,7 +2249,7 @@
         <v>267</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2254,7 +2263,7 @@
         <v>267</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2268,7 +2277,7 @@
         <v>267</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2279,10 +2288,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2296,7 +2305,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2310,7 +2319,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2324,7 +2333,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2338,7 +2347,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2352,7 +2361,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2366,7 +2375,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2380,7 +2389,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2394,7 +2403,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2408,7 +2417,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2422,7 +2431,7 @@
         <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2436,7 +2445,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2450,7 +2459,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2464,7 +2473,7 @@
         <v>267</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2478,7 +2487,7 @@
         <v>267</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2489,10 +2498,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2506,7 +2515,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2520,7 +2529,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2534,7 +2543,7 @@
         <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2545,10 +2554,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2562,7 +2571,7 @@
         <v>267</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2576,7 +2585,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2587,10 +2596,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2604,7 +2613,7 @@
         <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2618,7 +2627,7 @@
         <v>267</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2632,7 +2641,7 @@
         <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2646,7 +2655,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2660,7 +2669,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2674,7 +2683,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2688,7 +2697,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2702,7 +2711,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2716,7 +2725,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2730,7 +2739,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2744,7 +2753,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2758,7 +2767,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2772,7 +2781,7 @@
         <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2786,7 +2795,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2800,7 +2809,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2814,7 +2823,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2825,10 +2834,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2842,7 +2851,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2856,7 +2865,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2867,10 +2876,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2884,7 +2893,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2898,7 +2907,7 @@
         <v>267</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2912,7 +2921,7 @@
         <v>267</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2926,7 +2935,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2940,7 +2949,7 @@
         <v>266</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2954,7 +2963,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2965,10 +2974,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D73" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2979,10 +2988,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2996,7 +3005,7 @@
         <v>267</v>
       </c>
       <c r="D75" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3007,10 +3016,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3024,7 +3033,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3038,7 +3047,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3052,7 +3061,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3066,7 +3075,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3080,7 +3089,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3094,7 +3103,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3105,10 +3114,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D83" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3119,10 +3128,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D84" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3133,10 +3142,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3147,10 +3156,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3161,10 +3170,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3175,10 +3184,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3192,7 +3201,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3206,7 +3215,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3220,7 +3229,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3234,7 +3243,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3248,7 +3257,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3262,7 +3271,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3276,7 +3285,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3290,7 +3299,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3304,7 +3313,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3318,7 +3327,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3332,7 +3341,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3346,7 +3355,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3360,7 +3369,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3374,7 +3383,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3388,7 +3397,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3402,7 +3411,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3416,7 +3425,7 @@
         <v>266</v>
       </c>
       <c r="D105" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3430,7 +3439,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3444,7 +3453,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3458,7 +3467,7 @@
         <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3472,7 +3481,7 @@
         <v>267</v>
       </c>
       <c r="D109" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3486,7 +3495,7 @@
         <v>267</v>
       </c>
       <c r="D110" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3497,10 +3506,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D111" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3514,7 +3523,7 @@
         <v>267</v>
       </c>
       <c r="D112" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3528,7 +3537,7 @@
         <v>267</v>
       </c>
       <c r="D113" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3542,7 +3551,7 @@
         <v>267</v>
       </c>
       <c r="D114" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3556,7 +3565,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3570,7 +3579,7 @@
         <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3584,7 +3593,7 @@
         <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3598,7 +3607,7 @@
         <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3612,7 +3621,7 @@
         <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3623,10 +3632,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D120" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3640,7 +3649,7 @@
         <v>267</v>
       </c>
       <c r="D121" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3654,7 +3663,7 @@
         <v>267</v>
       </c>
       <c r="D122" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3668,7 +3677,7 @@
         <v>267</v>
       </c>
       <c r="D123" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3682,7 +3691,7 @@
         <v>267</v>
       </c>
       <c r="D124" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3696,7 +3705,7 @@
         <v>267</v>
       </c>
       <c r="D125" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3710,7 +3719,7 @@
         <v>267</v>
       </c>
       <c r="D126" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3724,7 +3733,7 @@
         <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3738,7 +3747,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3752,7 +3761,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3766,7 +3775,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3780,7 +3789,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3794,7 +3803,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3808,7 +3817,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3822,7 +3831,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3836,7 +3845,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3847,10 +3856,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D136" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3861,10 +3870,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D137" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3878,7 +3887,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3892,7 +3901,7 @@
         <v>266</v>
       </c>
       <c r="D139" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3906,7 +3915,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3917,10 +3926,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D141" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3934,7 +3943,7 @@
         <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3948,7 +3957,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3962,7 +3971,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3976,7 +3985,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3990,7 +3999,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4004,7 +4013,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4015,10 +4024,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D148" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4032,7 +4041,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4046,7 +4055,7 @@
         <v>267</v>
       </c>
       <c r="D150" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4060,7 +4069,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4074,7 +4083,7 @@
         <v>267</v>
       </c>
       <c r="D152" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4088,7 +4097,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4102,7 +4111,7 @@
         <v>266</v>
       </c>
       <c r="D154" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4116,7 +4125,7 @@
         <v>266</v>
       </c>
       <c r="D155" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4130,7 +4139,7 @@
         <v>266</v>
       </c>
       <c r="D156" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4144,7 +4153,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4158,7 +4167,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4172,7 +4181,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4186,7 +4195,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4200,7 +4209,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4214,7 +4223,7 @@
         <v>267</v>
       </c>
       <c r="D162" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4228,7 +4237,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4242,7 +4251,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4256,7 +4265,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4270,7 +4279,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4284,7 +4293,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4298,7 +4307,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4312,7 +4321,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4326,7 +4335,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4340,7 +4349,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4354,7 +4363,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4368,7 +4377,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4382,7 +4391,7 @@
         <v>267</v>
       </c>
       <c r="D174" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4396,7 +4405,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4410,7 +4419,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4424,7 +4433,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4438,7 +4447,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4452,7 +4461,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4466,7 +4475,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4480,7 +4489,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4494,7 +4503,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4508,7 +4517,7 @@
         <v>266</v>
       </c>
       <c r="D183" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4522,7 +4531,7 @@
         <v>266</v>
       </c>
       <c r="D184" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4536,7 +4545,7 @@
         <v>266</v>
       </c>
       <c r="D185" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4547,10 +4556,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D186" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4564,7 +4573,7 @@
         <v>266</v>
       </c>
       <c r="D187" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4578,7 +4587,7 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4592,7 +4601,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4606,7 +4615,7 @@
         <v>266</v>
       </c>
       <c r="D190" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4620,7 +4629,7 @@
         <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4631,10 +4640,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D192" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4648,7 +4657,7 @@
         <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4662,7 +4671,7 @@
         <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4676,7 +4685,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4690,7 +4699,7 @@
         <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4704,7 +4713,7 @@
         <v>266</v>
       </c>
       <c r="D197" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4718,7 +4727,7 @@
         <v>267</v>
       </c>
       <c r="D198" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4732,7 +4741,7 @@
         <v>267</v>
       </c>
       <c r="D199" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4746,7 +4755,7 @@
         <v>267</v>
       </c>
       <c r="D200" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4760,7 +4769,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4774,7 +4783,7 @@
         <v>267</v>
       </c>
       <c r="D202" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4788,7 +4797,7 @@
         <v>267</v>
       </c>
       <c r="D203" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4802,7 +4811,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4816,7 +4825,7 @@
         <v>266</v>
       </c>
       <c r="D205" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4830,7 +4839,7 @@
         <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4844,7 +4853,7 @@
         <v>266</v>
       </c>
       <c r="D207" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4858,7 +4867,7 @@
         <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4872,7 +4881,7 @@
         <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4886,7 +4895,7 @@
         <v>266</v>
       </c>
       <c r="D210" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4900,7 +4909,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4914,7 +4923,7 @@
         <v>266</v>
       </c>
       <c r="D212" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4928,7 +4937,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4942,7 +4951,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4956,7 +4965,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4970,7 +4979,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4984,7 +4993,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4998,7 +5007,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5012,7 +5021,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5026,7 +5035,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5040,7 +5049,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5054,7 +5063,7 @@
         <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5068,7 +5077,7 @@
         <v>266</v>
       </c>
       <c r="D223" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5082,7 +5091,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5096,7 +5105,7 @@
         <v>266</v>
       </c>
       <c r="D225" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5110,7 +5119,7 @@
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5124,7 +5133,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5138,7 +5147,7 @@
         <v>266</v>
       </c>
       <c r="D228" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5152,7 +5161,7 @@
         <v>266</v>
       </c>
       <c r="D229" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5166,7 +5175,7 @@
         <v>266</v>
       </c>
       <c r="D230" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5180,7 +5189,7 @@
         <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5194,7 +5203,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5208,7 +5217,7 @@
         <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5222,7 +5231,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5236,7 +5245,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5250,7 +5259,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5264,7 +5273,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5278,7 +5287,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5292,7 +5301,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5306,7 +5315,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5320,7 +5329,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5334,7 +5343,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5348,7 +5357,7 @@
         <v>266</v>
       </c>
       <c r="D243" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5362,7 +5371,7 @@
         <v>266</v>
       </c>
       <c r="D244" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5376,7 +5385,7 @@
         <v>266</v>
       </c>
       <c r="D245" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5390,7 +5399,7 @@
         <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5404,7 +5413,7 @@
         <v>266</v>
       </c>
       <c r="D247" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5418,7 +5427,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5432,7 +5441,7 @@
         <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5446,7 +5455,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5460,7 +5469,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5474,7 +5483,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5488,7 +5497,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5502,7 +5511,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5516,7 +5525,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5530,7 +5539,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
